--- a/tools/hwtest/stack-watermark/CALC_SCANS/runs.xlsx
+++ b/tools/hwtest/stack-watermark/CALC_SCANS/runs.xlsx
@@ -43,6 +43,30 @@
     <col min="30" max="30" width="9" customWidth="1"/>
     <col min="31" max="31" width="9" customWidth="1"/>
     <col min="32" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="9" customWidth="1"/>
+    <col min="34" max="34" width="9" customWidth="1"/>
+    <col min="35" max="35" width="9" customWidth="1"/>
+    <col min="36" max="36" width="9" customWidth="1"/>
+    <col min="37" max="37" width="9" customWidth="1"/>
+    <col min="38" max="38" width="9" customWidth="1"/>
+    <col min="39" max="39" width="9" customWidth="1"/>
+    <col min="40" max="40" width="9" customWidth="1"/>
+    <col min="41" max="41" width="9" customWidth="1"/>
+    <col min="42" max="42" width="9" customWidth="1"/>
+    <col min="43" max="43" width="9" customWidth="1"/>
+    <col min="44" max="44" width="9" customWidth="1"/>
+    <col min="45" max="45" width="9" customWidth="1"/>
+    <col min="46" max="46" width="9" customWidth="1"/>
+    <col min="47" max="47" width="9" customWidth="1"/>
+    <col min="48" max="48" width="9" customWidth="1"/>
+    <col min="49" max="49" width="9" customWidth="1"/>
+    <col min="50" max="50" width="9" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="9" customWidth="1"/>
+    <col min="53" max="53" width="9" customWidth="1"/>
+    <col min="54" max="54" width="9" customWidth="1"/>
+    <col min="55" max="55" width="9" customWidth="1"/>
+    <col min="56" max="56" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -206,6 +230,126 @@
           <t>2026-07-30_002 SIM merged/1 ms/call</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+ stack</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+ status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+ span</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+ tenths</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+ calls</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+ ms/call</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+ stack</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+ status</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+ span</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+ tenths</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+ calls</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+ ms/call</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+ stack</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+ status</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+ span</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+ tenths</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+ calls</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+ ms/call</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+ stack</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+ status</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+ span</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+ tenths</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+ calls</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+ ms/call</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -308,6 +452,78 @@
       <c r="AF2">
         <f>IF(AE2=0,"",AD2*100/AE2-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>9</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>10</v>
+      </c>
+      <c r="AK2">
+        <v>60</v>
+      </c>
+      <c r="AL2">
+        <f>IF(AK2=0,"",AJ2*100/AK2-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>9</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>24</v>
+      </c>
+      <c r="AR2">
+        <f>IF(AQ2=0,"",AP2*100/AQ2-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS2">
+        <v>2092</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>16384</v>
+      </c>
+      <c r="AV2">
+        <v>10</v>
+      </c>
+      <c r="AW2">
+        <v>58</v>
+      </c>
+      <c r="AX2">
+        <f>IF(AW2=0,"",AV2*100/AW2-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY2">
+        <v>2052</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>8088</v>
+      </c>
+      <c r="BB2">
+        <v>10</v>
+      </c>
+      <c r="BC2">
+        <v>24</v>
+      </c>
+      <c r="BD2">
+        <f>IF(BC2=0,"",BB2*100/BC2-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -410,6 +626,78 @@
       <c r="AF3">
         <f>IF(AE3=0,"",AD3*100/AE3-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>9</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>10</v>
+      </c>
+      <c r="AK3">
+        <v>56</v>
+      </c>
+      <c r="AL3">
+        <f>IF(AK3=0,"",AJ3*100/AK3-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>9</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>10</v>
+      </c>
+      <c r="AQ3">
+        <v>24</v>
+      </c>
+      <c r="AR3">
+        <f>IF(AQ3=0,"",AP3*100/AQ3-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS3">
+        <v>2048</v>
+      </c>
+      <c r="AT3">
+        <v>2</v>
+      </c>
+      <c r="AU3">
+        <v>16384</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>57</v>
+      </c>
+      <c r="AX3">
+        <f>IF(AW3=0,"",AV3*100/AW3-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY3">
+        <v>2052</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>8088</v>
+      </c>
+      <c r="BB3">
+        <v>10</v>
+      </c>
+      <c r="BC3">
+        <v>23</v>
+      </c>
+      <c r="BD3">
+        <f>IF(BC3=0,"",BB3*100/BC3-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,6 +800,78 @@
       <c r="AF4">
         <f>IF(AE4=0,"",AD4*100/AE4-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>9</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>10</v>
+      </c>
+      <c r="AK4">
+        <v>56</v>
+      </c>
+      <c r="AL4">
+        <f>IF(AK4=0,"",AJ4*100/AK4-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>9</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>10</v>
+      </c>
+      <c r="AQ4">
+        <v>22</v>
+      </c>
+      <c r="AR4">
+        <f>IF(AQ4=0,"",AP4*100/AQ4-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS4">
+        <v>2048</v>
+      </c>
+      <c r="AT4">
+        <v>2</v>
+      </c>
+      <c r="AU4">
+        <v>16384</v>
+      </c>
+      <c r="AV4">
+        <v>10</v>
+      </c>
+      <c r="AW4">
+        <v>55</v>
+      </c>
+      <c r="AX4">
+        <f>IF(AW4=0,"",AV4*100/AW4-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY4">
+        <v>2048</v>
+      </c>
+      <c r="AZ4">
+        <v>2</v>
+      </c>
+      <c r="BA4">
+        <v>8088</v>
+      </c>
+      <c r="BB4">
+        <v>10</v>
+      </c>
+      <c r="BC4">
+        <v>23</v>
+      </c>
+      <c r="BD4">
+        <f>IF(BC4=0,"",BB4*100/BC4-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,6 +974,78 @@
       <c r="AF5">
         <f>IF(AE5=0,"",AD5*100/AE5-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>9</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>10</v>
+      </c>
+      <c r="AK5">
+        <v>57</v>
+      </c>
+      <c r="AL5">
+        <f>IF(AK5=0,"",AJ5*100/AK5-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>9</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <v>24</v>
+      </c>
+      <c r="AR5">
+        <f>IF(AQ5=0,"",AP5*100/AQ5-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS5">
+        <v>2048</v>
+      </c>
+      <c r="AT5">
+        <v>2</v>
+      </c>
+      <c r="AU5">
+        <v>16384</v>
+      </c>
+      <c r="AV5">
+        <v>10</v>
+      </c>
+      <c r="AW5">
+        <v>56</v>
+      </c>
+      <c r="AX5">
+        <f>IF(AW5=0,"",AV5*100/AW5-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY5">
+        <v>2388</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>8088</v>
+      </c>
+      <c r="BB5">
+        <v>10</v>
+      </c>
+      <c r="BC5">
+        <v>23</v>
+      </c>
+      <c r="BD5">
+        <f>IF(BC5=0,"",BB5*100/BC5-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,6 +1148,78 @@
       <c r="AF6">
         <f>IF(AE6=0,"",AD6*100/AE6-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>9</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>10</v>
+      </c>
+      <c r="AK6">
+        <v>55</v>
+      </c>
+      <c r="AL6">
+        <f>IF(AK6=0,"",AJ6*100/AK6-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>9</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>10</v>
+      </c>
+      <c r="AQ6">
+        <v>23</v>
+      </c>
+      <c r="AR6">
+        <f>IF(AQ6=0,"",AP6*100/AQ6-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS6">
+        <v>2076</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>16384</v>
+      </c>
+      <c r="AV6">
+        <v>10</v>
+      </c>
+      <c r="AW6">
+        <v>54</v>
+      </c>
+      <c r="AX6">
+        <f>IF(AW6=0,"",AV6*100/AW6-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY6">
+        <v>2076</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>8088</v>
+      </c>
+      <c r="BB6">
+        <v>10</v>
+      </c>
+      <c r="BC6">
+        <v>23</v>
+      </c>
+      <c r="BD6">
+        <f>IF(BC6=0,"",BB6*100/BC6-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -818,6 +1322,78 @@
       <c r="AF7">
         <f>IF(AE7=0,"",AD7*100/AE7-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>9</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>10</v>
+      </c>
+      <c r="AK7">
+        <v>41</v>
+      </c>
+      <c r="AL7">
+        <f>IF(AK7=0,"",AJ7*100/AK7-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>9</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>10</v>
+      </c>
+      <c r="AQ7">
+        <v>18</v>
+      </c>
+      <c r="AR7">
+        <f>IF(AQ7=0,"",AP7*100/AQ7-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS7">
+        <v>4112</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>16384</v>
+      </c>
+      <c r="AV7">
+        <v>10</v>
+      </c>
+      <c r="AW7">
+        <v>40</v>
+      </c>
+      <c r="AX7">
+        <f>IF(AW7=0,"",AV7*100/AW7-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY7">
+        <v>3948</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>8088</v>
+      </c>
+      <c r="BB7">
+        <v>10</v>
+      </c>
+      <c r="BC7">
+        <v>18</v>
+      </c>
+      <c r="BD7">
+        <f>IF(BC7=0,"",BB7*100/BC7-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -920,6 +1496,78 @@
       <c r="AF8">
         <f>IF(AE8=0,"",AD8*100/AE8-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>9</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>10</v>
+      </c>
+      <c r="AK8">
+        <v>40</v>
+      </c>
+      <c r="AL8">
+        <f>IF(AK8=0,"",AJ8*100/AK8-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>9</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>15</v>
+      </c>
+      <c r="AR8">
+        <f>IF(AQ8=0,"",AP8*100/AQ8-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS8">
+        <v>4276</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>16384</v>
+      </c>
+      <c r="AV8">
+        <v>10</v>
+      </c>
+      <c r="AW8">
+        <v>38</v>
+      </c>
+      <c r="AX8">
+        <f>IF(AW8=0,"",AV8*100/AW8-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY8">
+        <v>4220</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>8088</v>
+      </c>
+      <c r="BB8">
+        <v>10</v>
+      </c>
+      <c r="BC8">
+        <v>16</v>
+      </c>
+      <c r="BD8">
+        <f>IF(BC8=0,"",BB8*100/BC8-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1022,6 +1670,78 @@
       <c r="AF9">
         <f>IF(AE9=0,"",AD9*100/AE9-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>9</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>10</v>
+      </c>
+      <c r="AK9">
+        <v>37</v>
+      </c>
+      <c r="AL9">
+        <f>IF(AK9=0,"",AJ9*100/AK9-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>9</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>10</v>
+      </c>
+      <c r="AQ9">
+        <v>15</v>
+      </c>
+      <c r="AR9">
+        <f>IF(AQ9=0,"",AP9*100/AQ9-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS9">
+        <v>4564</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>16384</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>36</v>
+      </c>
+      <c r="AX9">
+        <f>IF(AW9=0,"",AV9*100/AW9-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY9">
+        <v>4612</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>8088</v>
+      </c>
+      <c r="BB9">
+        <v>10</v>
+      </c>
+      <c r="BC9">
+        <v>15</v>
+      </c>
+      <c r="BD9">
+        <f>IF(BC9=0,"",BB9*100/BC9-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1124,6 +1844,78 @@
       <c r="AF10">
         <f>IF(AE10=0,"",AD10*100/AE10-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>9</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>10</v>
+      </c>
+      <c r="AK10">
+        <v>18</v>
+      </c>
+      <c r="AL10">
+        <f>IF(AK10=0,"",AJ10*100/AK10-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>9</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>10</v>
+      </c>
+      <c r="AQ10">
+        <v>8</v>
+      </c>
+      <c r="AR10">
+        <f>IF(AQ10=0,"",AP10*100/AQ10-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS10">
+        <v>5124</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>16384</v>
+      </c>
+      <c r="AV10">
+        <v>10</v>
+      </c>
+      <c r="AW10">
+        <v>18</v>
+      </c>
+      <c r="AX10">
+        <f>IF(AW10=0,"",AV10*100/AW10-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY10">
+        <v>5068</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>8088</v>
+      </c>
+      <c r="BB10">
+        <v>10</v>
+      </c>
+      <c r="BC10">
+        <v>8</v>
+      </c>
+      <c r="BD10">
+        <f>IF(BC10=0,"",BB10*100/BC10-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1226,6 +2018,78 @@
       <c r="AF11">
         <f>IF(AE11=0,"",AD11*100/AE11-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>9</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>10</v>
+      </c>
+      <c r="AK11">
+        <v>54</v>
+      </c>
+      <c r="AL11">
+        <f>IF(AK11=0,"",AJ11*100/AK11-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>9</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>10</v>
+      </c>
+      <c r="AQ11">
+        <v>22</v>
+      </c>
+      <c r="AR11">
+        <f>IF(AQ11=0,"",AP11*100/AQ11-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS11">
+        <v>2328</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>16384</v>
+      </c>
+      <c r="AV11">
+        <v>10</v>
+      </c>
+      <c r="AW11">
+        <v>53</v>
+      </c>
+      <c r="AX11">
+        <f>IF(AW11=0,"",AV11*100/AW11-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY11">
+        <v>2328</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>8088</v>
+      </c>
+      <c r="BB11">
+        <v>10</v>
+      </c>
+      <c r="BC11">
+        <v>22</v>
+      </c>
+      <c r="BD11">
+        <f>IF(BC11=0,"",BB11*100/BC11-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1328,6 +2192,78 @@
       <c r="AF12">
         <f>IF(AE12=0,"",AD12*100/AE12-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>9</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>10</v>
+      </c>
+      <c r="AK12">
+        <v>52</v>
+      </c>
+      <c r="AL12">
+        <f>IF(AK12=0,"",AJ12*100/AK12-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>9</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>10</v>
+      </c>
+      <c r="AQ12">
+        <v>21</v>
+      </c>
+      <c r="AR12">
+        <f>IF(AQ12=0,"",AP12*100/AQ12-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS12">
+        <v>2344</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>16384</v>
+      </c>
+      <c r="AV12">
+        <v>10</v>
+      </c>
+      <c r="AW12">
+        <v>56</v>
+      </c>
+      <c r="AX12">
+        <f>IF(AW12=0,"",AV12*100/AW12-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY12">
+        <v>2344</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>8088</v>
+      </c>
+      <c r="BB12">
+        <v>10</v>
+      </c>
+      <c r="BC12">
+        <v>22</v>
+      </c>
+      <c r="BD12">
+        <f>IF(BC12=0,"",BB12*100/BC12-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1430,6 +2366,78 @@
       <c r="AF13">
         <f>IF(AE13=0,"",AD13*100/AE13-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>9</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>10</v>
+      </c>
+      <c r="AK13">
+        <v>52</v>
+      </c>
+      <c r="AL13">
+        <f>IF(AK13=0,"",AJ13*100/AK13-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>9</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>10</v>
+      </c>
+      <c r="AQ13">
+        <v>21</v>
+      </c>
+      <c r="AR13">
+        <f>IF(AQ13=0,"",AP13*100/AQ13-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS13">
+        <v>2204</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>16384</v>
+      </c>
+      <c r="AV13">
+        <v>10</v>
+      </c>
+      <c r="AW13">
+        <v>51</v>
+      </c>
+      <c r="AX13">
+        <f>IF(AW13=0,"",AV13*100/AW13-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY13">
+        <v>2208</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>8088</v>
+      </c>
+      <c r="BB13">
+        <v>10</v>
+      </c>
+      <c r="BC13">
+        <v>22</v>
+      </c>
+      <c r="BD13">
+        <f>IF(BC13=0,"",BB13*100/BC13-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1532,6 +2540,78 @@
       <c r="AF14">
         <f>IF(AE14=0,"",AD14*100/AE14-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>9</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>10</v>
+      </c>
+      <c r="AK14">
+        <v>18</v>
+      </c>
+      <c r="AL14">
+        <f>IF(AK14=0,"",AJ14*100/AK14-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>9</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>10</v>
+      </c>
+      <c r="AQ14">
+        <v>14</v>
+      </c>
+      <c r="AR14">
+        <f>IF(AQ14=0,"",AP14*100/AQ14-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS14">
+        <v>2420</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>16384</v>
+      </c>
+      <c r="AV14">
+        <v>10</v>
+      </c>
+      <c r="AW14">
+        <v>19</v>
+      </c>
+      <c r="AX14">
+        <f>IF(AW14=0,"",AV14*100/AW14-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY14">
+        <v>2396</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>8088</v>
+      </c>
+      <c r="BB14">
+        <v>10</v>
+      </c>
+      <c r="BC14">
+        <v>14</v>
+      </c>
+      <c r="BD14">
+        <f>IF(BC14=0,"",BB14*100/BC14-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1634,6 +2714,78 @@
       <c r="AF15">
         <f>IF(AE15=0,"",AD15*100/AE15-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>9</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>10</v>
+      </c>
+      <c r="AK15">
+        <v>52</v>
+      </c>
+      <c r="AL15">
+        <f>IF(AK15=0,"",AJ15*100/AK15-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>9</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>10</v>
+      </c>
+      <c r="AQ15">
+        <v>21</v>
+      </c>
+      <c r="AR15">
+        <f>IF(AQ15=0,"",AP15*100/AQ15-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS15">
+        <v>2776</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>16384</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>51</v>
+      </c>
+      <c r="AX15">
+        <f>IF(AW15=0,"",AV15*100/AW15-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY15">
+        <v>2776</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>8088</v>
+      </c>
+      <c r="BB15">
+        <v>10</v>
+      </c>
+      <c r="BC15">
+        <v>22</v>
+      </c>
+      <c r="BD15">
+        <f>IF(BC15=0,"",BB15*100/BC15-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1736,6 +2888,78 @@
       <c r="AF16">
         <f>IF(AE16=0,"",AD16*100/AE16-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>9</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>10</v>
+      </c>
+      <c r="AK16">
+        <v>54</v>
+      </c>
+      <c r="AL16">
+        <f>IF(AK16=0,"",AJ16*100/AK16-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>9</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>10</v>
+      </c>
+      <c r="AQ16">
+        <v>23</v>
+      </c>
+      <c r="AR16">
+        <f>IF(AQ16=0,"",AP16*100/AQ16-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS16">
+        <v>2688</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>16384</v>
+      </c>
+      <c r="AV16">
+        <v>10</v>
+      </c>
+      <c r="AW16">
+        <v>54</v>
+      </c>
+      <c r="AX16">
+        <f>IF(AW16=0,"",AV16*100/AW16-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY16">
+        <v>2688</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>8088</v>
+      </c>
+      <c r="BB16">
+        <v>10</v>
+      </c>
+      <c r="BC16">
+        <v>21</v>
+      </c>
+      <c r="BD16">
+        <f>IF(BC16=0,"",BB16*100/BC16-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1838,6 +3062,78 @@
       <c r="AF17">
         <f>IF(AE17=0,"",AD17*100/AE17-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>9</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>10</v>
+      </c>
+      <c r="AK17">
+        <v>50</v>
+      </c>
+      <c r="AL17">
+        <f>IF(AK17=0,"",AJ17*100/AK17-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>9</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>10</v>
+      </c>
+      <c r="AQ17">
+        <v>21</v>
+      </c>
+      <c r="AR17">
+        <f>IF(AQ17=0,"",AP17*100/AQ17-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS17">
+        <v>2976</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>16384</v>
+      </c>
+      <c r="AV17">
+        <v>10</v>
+      </c>
+      <c r="AW17">
+        <v>49</v>
+      </c>
+      <c r="AX17">
+        <f>IF(AW17=0,"",AV17*100/AW17-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY17">
+        <v>3068</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>8088</v>
+      </c>
+      <c r="BB17">
+        <v>10</v>
+      </c>
+      <c r="BC17">
+        <v>19</v>
+      </c>
+      <c r="BD17">
+        <f>IF(BC17=0,"",BB17*100/BC17-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1940,6 +3236,78 @@
       <c r="AF18">
         <f>IF(AE18=0,"",AD18*100/AE18-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>9</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>10</v>
+      </c>
+      <c r="AK18">
+        <v>51</v>
+      </c>
+      <c r="AL18">
+        <f>IF(AK18=0,"",AJ18*100/AK18-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>9</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>10</v>
+      </c>
+      <c r="AQ18">
+        <v>21</v>
+      </c>
+      <c r="AR18">
+        <f>IF(AQ18=0,"",AP18*100/AQ18-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS18">
+        <v>2544</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>16384</v>
+      </c>
+      <c r="AV18">
+        <v>10</v>
+      </c>
+      <c r="AW18">
+        <v>49</v>
+      </c>
+      <c r="AX18">
+        <f>IF(AW18=0,"",AV18*100/AW18-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY18">
+        <v>2520</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>8088</v>
+      </c>
+      <c r="BB18">
+        <v>10</v>
+      </c>
+      <c r="BC18">
+        <v>19</v>
+      </c>
+      <c r="BD18">
+        <f>IF(BC18=0,"",BB18*100/BC18-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2042,6 +3410,78 @@
       <c r="AF19">
         <f>IF(AE19=0,"",AD19*100/AE19-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>9</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>10</v>
+      </c>
+      <c r="AK19">
+        <v>49</v>
+      </c>
+      <c r="AL19">
+        <f>IF(AK19=0,"",AJ19*100/AK19-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>9</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>10</v>
+      </c>
+      <c r="AQ19">
+        <v>22</v>
+      </c>
+      <c r="AR19">
+        <f>IF(AQ19=0,"",AP19*100/AQ19-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS19">
+        <v>2148</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>16384</v>
+      </c>
+      <c r="AV19">
+        <v>10</v>
+      </c>
+      <c r="AW19">
+        <v>49</v>
+      </c>
+      <c r="AX19">
+        <f>IF(AW19=0,"",AV19*100/AW19-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY19">
+        <v>2144</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>8088</v>
+      </c>
+      <c r="BB19">
+        <v>10</v>
+      </c>
+      <c r="BC19">
+        <v>20</v>
+      </c>
+      <c r="BD19">
+        <f>IF(BC19=0,"",BB19*100/BC19-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2144,6 +3584,78 @@
       <c r="AF20">
         <f>IF(AE20=0,"",AD20*100/AE20-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>9</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>10</v>
+      </c>
+      <c r="AK20">
+        <v>52</v>
+      </c>
+      <c r="AL20">
+        <f>IF(AK20=0,"",AJ20*100/AK20-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>9</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>10</v>
+      </c>
+      <c r="AQ20">
+        <v>22</v>
+      </c>
+      <c r="AR20">
+        <f>IF(AQ20=0,"",AP20*100/AQ20-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS20">
+        <v>3704</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>16384</v>
+      </c>
+      <c r="AV20">
+        <v>10</v>
+      </c>
+      <c r="AW20">
+        <v>49</v>
+      </c>
+      <c r="AX20">
+        <f>IF(AW20=0,"",AV20*100/AW20-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY20">
+        <v>3908</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>8088</v>
+      </c>
+      <c r="BB20">
+        <v>10</v>
+      </c>
+      <c r="BC20">
+        <v>20</v>
+      </c>
+      <c r="BD20">
+        <f>IF(BC20=0,"",BB20*100/BC20-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2246,6 +3758,78 @@
       <c r="AF21">
         <f>IF(AE21=0,"",AD21*100/AE21-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>9</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>10</v>
+      </c>
+      <c r="AK21">
+        <v>51</v>
+      </c>
+      <c r="AL21">
+        <f>IF(AK21=0,"",AJ21*100/AK21-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>9</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>10</v>
+      </c>
+      <c r="AQ21">
+        <v>21</v>
+      </c>
+      <c r="AR21">
+        <f>IF(AQ21=0,"",AP21*100/AQ21-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS21">
+        <v>3456</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>16384</v>
+      </c>
+      <c r="AV21">
+        <v>10</v>
+      </c>
+      <c r="AW21">
+        <v>52</v>
+      </c>
+      <c r="AX21">
+        <f>IF(AW21=0,"",AV21*100/AW21-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY21">
+        <v>3456</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>8088</v>
+      </c>
+      <c r="BB21">
+        <v>10</v>
+      </c>
+      <c r="BC21">
+        <v>20</v>
+      </c>
+      <c r="BD21">
+        <f>IF(BC21=0,"",BB21*100/BC21-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2348,6 +3932,78 @@
       <c r="AF22">
         <f>IF(AE22=0,"",AD22*100/AE22-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>9</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>10</v>
+      </c>
+      <c r="AK22">
+        <v>50</v>
+      </c>
+      <c r="AL22">
+        <f>IF(AK22=0,"",AJ22*100/AK22-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>9</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>10</v>
+      </c>
+      <c r="AQ22">
+        <v>20</v>
+      </c>
+      <c r="AR22">
+        <f>IF(AQ22=0,"",AP22*100/AQ22-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS22">
+        <v>2052</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>16384</v>
+      </c>
+      <c r="AV22">
+        <v>10</v>
+      </c>
+      <c r="AW22">
+        <v>52</v>
+      </c>
+      <c r="AX22">
+        <f>IF(AW22=0,"",AV22*100/AW22-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY22">
+        <v>2052</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>8088</v>
+      </c>
+      <c r="BB22">
+        <v>10</v>
+      </c>
+      <c r="BC22">
+        <v>20</v>
+      </c>
+      <c r="BD22">
+        <f>IF(BC22=0,"",BB22*100/BC22-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2450,6 +4106,78 @@
       <c r="AF23">
         <f>IF(AE23=0,"",AD23*100/AE23-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>9</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>10</v>
+      </c>
+      <c r="AK23">
+        <v>50</v>
+      </c>
+      <c r="AL23">
+        <f>IF(AK23=0,"",AJ23*100/AK23-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>9</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>10</v>
+      </c>
+      <c r="AQ23">
+        <v>21</v>
+      </c>
+      <c r="AR23">
+        <f>IF(AQ23=0,"",AP23*100/AQ23-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS23">
+        <v>2052</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>16384</v>
+      </c>
+      <c r="AV23">
+        <v>10</v>
+      </c>
+      <c r="AW23">
+        <v>50</v>
+      </c>
+      <c r="AX23">
+        <f>IF(AW23=0,"",AV23*100/AW23-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY23">
+        <v>2048</v>
+      </c>
+      <c r="AZ23">
+        <v>2</v>
+      </c>
+      <c r="BA23">
+        <v>8088</v>
+      </c>
+      <c r="BB23">
+        <v>10</v>
+      </c>
+      <c r="BC23">
+        <v>21</v>
+      </c>
+      <c r="BD23">
+        <f>IF(BC23=0,"",BB23*100/BC23-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2552,6 +4280,78 @@
       <c r="AF24">
         <f>IF(AE24=0,"",AD24*100/AE24-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>9</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>10</v>
+      </c>
+      <c r="AK24">
+        <v>51</v>
+      </c>
+      <c r="AL24">
+        <f>IF(AK24=0,"",AJ24*100/AK24-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>9</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>10</v>
+      </c>
+      <c r="AQ24">
+        <v>22</v>
+      </c>
+      <c r="AR24">
+        <f>IF(AQ24=0,"",AP24*100/AQ24-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS24">
+        <v>2120</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>16384</v>
+      </c>
+      <c r="AV24">
+        <v>10</v>
+      </c>
+      <c r="AW24">
+        <v>49</v>
+      </c>
+      <c r="AX24">
+        <f>IF(AW24=0,"",AV24*100/AW24-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY24">
+        <v>2120</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>8088</v>
+      </c>
+      <c r="BB24">
+        <v>10</v>
+      </c>
+      <c r="BC24">
+        <v>20</v>
+      </c>
+      <c r="BD24">
+        <f>IF(BC24=0,"",BB24*100/BC24-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2654,6 +4454,78 @@
       <c r="AF25">
         <f>IF(AE25=0,"",AD25*100/AE25-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>9</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>10</v>
+      </c>
+      <c r="AK25">
+        <v>51</v>
+      </c>
+      <c r="AL25">
+        <f>IF(AK25=0,"",AJ25*100/AK25-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>9</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>10</v>
+      </c>
+      <c r="AQ25">
+        <v>20</v>
+      </c>
+      <c r="AR25">
+        <f>IF(AQ25=0,"",AP25*100/AQ25-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS25">
+        <v>3488</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>16384</v>
+      </c>
+      <c r="AV25">
+        <v>10</v>
+      </c>
+      <c r="AW25">
+        <v>52</v>
+      </c>
+      <c r="AX25">
+        <f>IF(AW25=0,"",AV25*100/AW25-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY25">
+        <v>3488</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>8088</v>
+      </c>
+      <c r="BB25">
+        <v>10</v>
+      </c>
+      <c r="BC25">
+        <v>20</v>
+      </c>
+      <c r="BD25">
+        <f>IF(BC25=0,"",BB25*100/BC25-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2756,6 +4628,78 @@
       <c r="AF26">
         <f>IF(AE26=0,"",AD26*100/AE26-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>9</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>10</v>
+      </c>
+      <c r="AK26">
+        <v>26</v>
+      </c>
+      <c r="AL26">
+        <f>IF(AK26=0,"",AJ26*100/AK26-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>9</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>10</v>
+      </c>
+      <c r="AQ26">
+        <v>11</v>
+      </c>
+      <c r="AR26">
+        <f>IF(AQ26=0,"",AP26*100/AQ26-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS26">
+        <v>4652</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>16384</v>
+      </c>
+      <c r="AV26">
+        <v>10</v>
+      </c>
+      <c r="AW26">
+        <v>26</v>
+      </c>
+      <c r="AX26">
+        <f>IF(AW26=0,"",AV26*100/AW26-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY26">
+        <v>4644</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>8088</v>
+      </c>
+      <c r="BB26">
+        <v>10</v>
+      </c>
+      <c r="BC26">
+        <v>11</v>
+      </c>
+      <c r="BD26">
+        <f>IF(BC26=0,"",BB26*100/BC26-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2858,6 +4802,78 @@
       <c r="AF27">
         <f>IF(AE27=0,"",AD27*100/AE27-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>9</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>10</v>
+      </c>
+      <c r="AK27">
+        <v>48</v>
+      </c>
+      <c r="AL27">
+        <f>IF(AK27=0,"",AJ27*100/AK27-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>9</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>10</v>
+      </c>
+      <c r="AQ27">
+        <v>20</v>
+      </c>
+      <c r="AR27">
+        <f>IF(AQ27=0,"",AP27*100/AQ27-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS27">
+        <v>2048</v>
+      </c>
+      <c r="AT27">
+        <v>2</v>
+      </c>
+      <c r="AU27">
+        <v>16384</v>
+      </c>
+      <c r="AV27">
+        <v>10</v>
+      </c>
+      <c r="AW27">
+        <v>51</v>
+      </c>
+      <c r="AX27">
+        <f>IF(AW27=0,"",AV27*100/AW27-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY27">
+        <v>2048</v>
+      </c>
+      <c r="AZ27">
+        <v>2</v>
+      </c>
+      <c r="BA27">
+        <v>8088</v>
+      </c>
+      <c r="BB27">
+        <v>10</v>
+      </c>
+      <c r="BC27">
+        <v>20</v>
+      </c>
+      <c r="BD27">
+        <f>IF(BC27=0,"",BB27*100/BC27-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2960,6 +4976,78 @@
       <c r="AF28">
         <f>IF(AE28=0,"",AD28*100/AE28-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>9</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>11</v>
+      </c>
+      <c r="AK28">
+        <v>5</v>
+      </c>
+      <c r="AL28">
+        <f>IF(AK28=0,"",AJ28*100/AK28-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>9</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>14</v>
+      </c>
+      <c r="AQ28">
+        <v>3</v>
+      </c>
+      <c r="AR28">
+        <f>IF(AQ28=0,"",AP28*100/AQ28-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS28">
+        <v>4468</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>16384</v>
+      </c>
+      <c r="AV28">
+        <v>11</v>
+      </c>
+      <c r="AW28">
+        <v>5</v>
+      </c>
+      <c r="AX28">
+        <f>IF(AW28=0,"",AV28*100/AW28-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY28">
+        <v>4476</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>8088</v>
+      </c>
+      <c r="BB28">
+        <v>14</v>
+      </c>
+      <c r="BC28">
+        <v>3</v>
+      </c>
+      <c r="BD28">
+        <f>IF(BC28=0,"",BB28*100/BC28-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3044,6 +5132,78 @@
       <c r="AF29">
         <f>IF(AE29=0,"",AD29*100/AE29-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>9</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>10</v>
+      </c>
+      <c r="AK29">
+        <v>4</v>
+      </c>
+      <c r="AL29">
+        <f>IF(AK29=0,"",AJ29*100/AK29-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>9</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>11</v>
+      </c>
+      <c r="AQ29">
+        <v>2</v>
+      </c>
+      <c r="AR29">
+        <f>IF(AQ29=0,"",AP29*100/AQ29-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS29">
+        <v>5512</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>16384</v>
+      </c>
+      <c r="AV29">
+        <v>10</v>
+      </c>
+      <c r="AW29">
+        <v>4</v>
+      </c>
+      <c r="AX29">
+        <f>IF(AW29=0,"",AV29*100/AW29-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY29">
+        <v>5528</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>8088</v>
+      </c>
+      <c r="BB29">
+        <v>11</v>
+      </c>
+      <c r="BC29">
+        <v>2</v>
+      </c>
+      <c r="BD29">
+        <f>IF(BC29=0,"",BB29*100/BC29-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3128,6 +5288,78 @@
       <c r="AF30">
         <f>IF(AE30=0,"",AD30*100/AE30-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>9</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>12</v>
+      </c>
+      <c r="AK30">
+        <v>5</v>
+      </c>
+      <c r="AL30">
+        <f>IF(AK30=0,"",AJ30*100/AK30-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>9</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>10</v>
+      </c>
+      <c r="AQ30">
+        <v>2</v>
+      </c>
+      <c r="AR30">
+        <f>IF(AQ30=0,"",AP30*100/AQ30-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS30">
+        <v>4428</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>16384</v>
+      </c>
+      <c r="AV30">
+        <v>10</v>
+      </c>
+      <c r="AW30">
+        <v>4</v>
+      </c>
+      <c r="AX30">
+        <f>IF(AW30=0,"",AV30*100/AW30-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY30">
+        <v>4476</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>8088</v>
+      </c>
+      <c r="BB30">
+        <v>14</v>
+      </c>
+      <c r="BC30">
+        <v>3</v>
+      </c>
+      <c r="BD30">
+        <f>IF(BC30=0,"",BB30*100/BC30-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3212,6 +5444,78 @@
       <c r="AF31">
         <f>IF(AE31=0,"",AD31*100/AE31-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>9</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>10</v>
+      </c>
+      <c r="AK31">
+        <v>4</v>
+      </c>
+      <c r="AL31">
+        <f>IF(AK31=0,"",AJ31*100/AK31-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
+        <v>9</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>10</v>
+      </c>
+      <c r="AQ31">
+        <v>20</v>
+      </c>
+      <c r="AR31">
+        <f>IF(AQ31=0,"",AP31*100/AQ31-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS31">
+        <v>5428</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31">
+        <v>16384</v>
+      </c>
+      <c r="AV31">
+        <v>10</v>
+      </c>
+      <c r="AW31">
+        <v>4</v>
+      </c>
+      <c r="AX31">
+        <f>IF(AW31=0,"",AV31*100/AW31-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY31">
+        <v>2052</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>8088</v>
+      </c>
+      <c r="BB31">
+        <v>10</v>
+      </c>
+      <c r="BC31">
+        <v>21</v>
+      </c>
+      <c r="BD31">
+        <f>IF(BC31=0,"",BB31*100/BC31-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3296,6 +5600,78 @@
       <c r="AF32">
         <f>IF(AE32=0,"",AD32*100/AE32-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>9</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>10</v>
+      </c>
+      <c r="AK32">
+        <v>33</v>
+      </c>
+      <c r="AL32">
+        <f>IF(AK32=0,"",AJ32*100/AK32-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>9</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>10</v>
+      </c>
+      <c r="AQ32">
+        <v>8</v>
+      </c>
+      <c r="AR32">
+        <f>IF(AQ32=0,"",AP32*100/AQ32-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS32">
+        <v>5388</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>16384</v>
+      </c>
+      <c r="AV32">
+        <v>10</v>
+      </c>
+      <c r="AW32">
+        <v>32</v>
+      </c>
+      <c r="AX32">
+        <f>IF(AW32=0,"",AV32*100/AW32-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY32">
+        <v>5868</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>8088</v>
+      </c>
+      <c r="BB32">
+        <v>10</v>
+      </c>
+      <c r="BC32">
+        <v>8</v>
+      </c>
+      <c r="BD32">
+        <f>IF(BC32=0,"",BB32*100/BC32-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3380,6 +5756,78 @@
       <c r="AF33">
         <f>IF(AE33=0,"",AD33*100/AE33-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>9</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>10</v>
+      </c>
+      <c r="AK33">
+        <v>45</v>
+      </c>
+      <c r="AL33">
+        <f>IF(AK33=0,"",AJ33*100/AK33-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>9</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>10</v>
+      </c>
+      <c r="AQ33">
+        <v>19</v>
+      </c>
+      <c r="AR33">
+        <f>IF(AQ33=0,"",AP33*100/AQ33-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS33">
+        <v>2048</v>
+      </c>
+      <c r="AT33">
+        <v>2</v>
+      </c>
+      <c r="AU33">
+        <v>16384</v>
+      </c>
+      <c r="AV33">
+        <v>10</v>
+      </c>
+      <c r="AW33">
+        <v>45</v>
+      </c>
+      <c r="AX33">
+        <f>IF(AW33=0,"",AV33*100/AW33-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY33">
+        <v>2052</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>8088</v>
+      </c>
+      <c r="BB33">
+        <v>10</v>
+      </c>
+      <c r="BC33">
+        <v>20</v>
+      </c>
+      <c r="BD33">
+        <f>IF(BC33=0,"",BB33*100/BC33-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3464,6 +5912,78 @@
       <c r="AF34">
         <f>IF(AE34=0,"",AD34*100/AE34-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34">
+        <v>9</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>11</v>
+      </c>
+      <c r="AK34">
+        <v>1</v>
+      </c>
+      <c r="AL34">
+        <f>IF(AK34=0,"",AJ34*100/AK34-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>9</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>12</v>
+      </c>
+      <c r="AQ34">
+        <v>1</v>
+      </c>
+      <c r="AR34">
+        <f>IF(AQ34=0,"",AP34*100/AQ34-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS34">
+        <v>3780</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>16384</v>
+      </c>
+      <c r="AV34">
+        <v>12</v>
+      </c>
+      <c r="AW34">
+        <v>1</v>
+      </c>
+      <c r="AX34">
+        <f>IF(AW34=0,"",AV34*100/AW34-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY34">
+        <v>3860</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>8088</v>
+      </c>
+      <c r="BB34">
+        <v>7</v>
+      </c>
+      <c r="BC34">
+        <v>1</v>
+      </c>
+      <c r="BD34">
+        <f>IF(BC34=0,"",BB34*100/BC34-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3530,6 +6050,78 @@
       <c r="AF35">
         <f>IF(AE35=0,"",AD35*100/AE35-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35">
+        <v>9</v>
+      </c>
+      <c r="AI35">
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <v>11</v>
+      </c>
+      <c r="AK35">
+        <v>4</v>
+      </c>
+      <c r="AL35">
+        <f>IF(AK35=0,"",AJ35*100/AK35-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>9</v>
+      </c>
+      <c r="AO35">
+        <v>0</v>
+      </c>
+      <c r="AP35">
+        <v>14</v>
+      </c>
+      <c r="AQ35">
+        <v>3</v>
+      </c>
+      <c r="AR35">
+        <f>IF(AQ35=0,"",AP35*100/AQ35-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS35">
+        <v>7724</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>16384</v>
+      </c>
+      <c r="AV35">
+        <v>11</v>
+      </c>
+      <c r="AW35">
+        <v>4</v>
+      </c>
+      <c r="AX35">
+        <f>IF(AW35=0,"",AV35*100/AW35-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY35">
+        <v>7676</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>8088</v>
+      </c>
+      <c r="BB35">
+        <v>13</v>
+      </c>
+      <c r="BC35">
+        <v>3</v>
+      </c>
+      <c r="BD35">
+        <f>IF(BC35=0,"",BB35*100/BC35-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3614,6 +6206,78 @@
       <c r="AF36">
         <f>IF(AE36=0,"",AD36*100/AE36-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>9</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>13</v>
+      </c>
+      <c r="AK36">
+        <v>2</v>
+      </c>
+      <c r="AL36">
+        <f>IF(AK36=0,"",AJ36*100/AK36-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>9</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>16</v>
+      </c>
+      <c r="AQ36">
+        <v>1</v>
+      </c>
+      <c r="AR36">
+        <f>IF(AQ36=0,"",AP36*100/AQ36-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS36">
+        <v>5668</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>16384</v>
+      </c>
+      <c r="AV36">
+        <v>14</v>
+      </c>
+      <c r="AW36">
+        <v>2</v>
+      </c>
+      <c r="AX36">
+        <f>IF(AW36=0,"",AV36*100/AW36-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY36">
+        <v>5676</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>8088</v>
+      </c>
+      <c r="BB36">
+        <v>16</v>
+      </c>
+      <c r="BC36">
+        <v>1</v>
+      </c>
+      <c r="BD36">
+        <f>IF(BC36=0,"",BB36*100/BC36-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3698,6 +6362,78 @@
       <c r="AF37">
         <f>IF(AE37=0,"",AD37*100/AE37-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>9</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>10</v>
+      </c>
+      <c r="AK37">
+        <v>3</v>
+      </c>
+      <c r="AL37">
+        <f>IF(AK37=0,"",AJ37*100/AK37-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>9</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>16</v>
+      </c>
+      <c r="AQ37">
+        <v>2</v>
+      </c>
+      <c r="AR37">
+        <f>IF(AQ37=0,"",AP37*100/AQ37-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS37">
+        <v>4516</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>16384</v>
+      </c>
+      <c r="AV37">
+        <v>10</v>
+      </c>
+      <c r="AW37">
+        <v>3</v>
+      </c>
+      <c r="AX37">
+        <f>IF(AW37=0,"",AV37*100/AW37-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY37">
+        <v>4548</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>8088</v>
+      </c>
+      <c r="BB37">
+        <v>15</v>
+      </c>
+      <c r="BC37">
+        <v>2</v>
+      </c>
+      <c r="BD37">
+        <f>IF(BC37=0,"",BB37*100/BC37-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3782,6 +6518,78 @@
       <c r="AF38">
         <f>IF(AE38=0,"",AD38*100/AE38-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>9</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>192</v>
+      </c>
+      <c r="AK38">
+        <v>1</v>
+      </c>
+      <c r="AL38">
+        <f>IF(AK38=0,"",AJ38*100/AK38-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>9</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>333</v>
+      </c>
+      <c r="AQ38">
+        <v>1</v>
+      </c>
+      <c r="AR38">
+        <f>IF(AQ38=0,"",AP38*100/AQ38-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS38">
+        <v>6308</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>16384</v>
+      </c>
+      <c r="AV38">
+        <v>192</v>
+      </c>
+      <c r="AW38">
+        <v>1</v>
+      </c>
+      <c r="AX38">
+        <f>IF(AW38=0,"",AV38*100/AW38-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY38">
+        <v>5844</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>8088</v>
+      </c>
+      <c r="BB38">
+        <v>334</v>
+      </c>
+      <c r="BC38">
+        <v>1</v>
+      </c>
+      <c r="BD38">
+        <f>IF(BC38=0,"",BB38*100/BC38-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3866,6 +6674,78 @@
       <c r="AF39">
         <f>IF(AE39=0,"",AD39*100/AE39-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>9</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>11</v>
+      </c>
+      <c r="AK39">
+        <v>3</v>
+      </c>
+      <c r="AL39">
+        <f>IF(AK39=0,"",AJ39*100/AK39-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>9</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>10</v>
+      </c>
+      <c r="AQ39">
+        <v>1</v>
+      </c>
+      <c r="AR39">
+        <f>IF(AQ39=0,"",AP39*100/AQ39-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS39">
+        <v>7772</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39">
+        <v>16384</v>
+      </c>
+      <c r="AV39">
+        <v>11</v>
+      </c>
+      <c r="AW39">
+        <v>3</v>
+      </c>
+      <c r="AX39">
+        <f>IF(AW39=0,"",AV39*100/AW39-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY39">
+        <v>7704</v>
+      </c>
+      <c r="AZ39">
+        <v>0</v>
+      </c>
+      <c r="BA39">
+        <v>8088</v>
+      </c>
+      <c r="BB39">
+        <v>10</v>
+      </c>
+      <c r="BC39">
+        <v>1</v>
+      </c>
+      <c r="BD39">
+        <f>IF(BC39=0,"",BB39*100/BC39-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3950,6 +6830,78 @@
       <c r="AF40">
         <f>IF(AE40=0,"",AD40*100/AE40-$AD$2*100/$AE$2)</f>
       </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>9</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>10</v>
+      </c>
+      <c r="AK40">
+        <v>46</v>
+      </c>
+      <c r="AL40">
+        <f>IF(AK40=0,"",AJ40*100/AK40-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
+        <v>9</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
+        <v>10</v>
+      </c>
+      <c r="AQ40">
+        <v>19</v>
+      </c>
+      <c r="AR40">
+        <f>IF(AQ40=0,"",AP40*100/AQ40-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS40">
+        <v>3200</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40">
+        <v>16384</v>
+      </c>
+      <c r="AV40">
+        <v>10</v>
+      </c>
+      <c r="AW40">
+        <v>44</v>
+      </c>
+      <c r="AX40">
+        <f>IF(AW40=0,"",AV40*100/AW40-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY40">
+        <v>3088</v>
+      </c>
+      <c r="AZ40">
+        <v>0</v>
+      </c>
+      <c r="BA40">
+        <v>8088</v>
+      </c>
+      <c r="BB40">
+        <v>10</v>
+      </c>
+      <c r="BC40">
+        <v>19</v>
+      </c>
+      <c r="BD40">
+        <f>IF(BC40=0,"",BB40*100/BC40-$BB$2*100/$BC$2)</f>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4033,6 +6985,78 @@
       </c>
       <c r="AF41">
         <f>IF(AE41=0,"",AD41*100/AE41-$AD$2*100/$AE$2)</f>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41">
+        <v>9</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>10</v>
+      </c>
+      <c r="AK41">
+        <v>29</v>
+      </c>
+      <c r="AL41">
+        <f>IF(AK41=0,"",AJ41*100/AK41-$AJ$2*100/$AK$2)</f>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>9</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>10</v>
+      </c>
+      <c r="AQ41">
+        <v>12</v>
+      </c>
+      <c r="AR41">
+        <f>IF(AQ41=0,"",AP41*100/AQ41-$AP$2*100/$AQ$2)</f>
+      </c>
+      <c r="AS41">
+        <v>4516</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41">
+        <v>16384</v>
+      </c>
+      <c r="AV41">
+        <v>10</v>
+      </c>
+      <c r="AW41">
+        <v>28</v>
+      </c>
+      <c r="AX41">
+        <f>IF(AW41=0,"",AV41*100/AW41-$AV$2*100/$AW$2)</f>
+      </c>
+      <c r="AY41">
+        <v>4556</v>
+      </c>
+      <c r="AZ41">
+        <v>0</v>
+      </c>
+      <c r="BA41">
+        <v>8088</v>
+      </c>
+      <c r="BB41">
+        <v>10</v>
+      </c>
+      <c r="BC41">
+        <v>12</v>
+      </c>
+      <c r="BD41">
+        <f>IF(BC41=0,"",BB41*100/BC41-$BB$2*100/$BC$2)</f>
       </c>
     </row>
   </sheetData>
@@ -4605,6 +7629,558 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20260731-02202023.bmp</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>12610</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2d6adaf59d0d7fbc708d13081d3f17088f2fbf4bcd294594c6c75a9eb977ced9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20260731-02202733.bmp</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>12610</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>08b99076996fe11fef7a2a04ae5d79425fc561734a1ce191f7a552f79cb54870</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20260731-02202836.bmp</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>12610</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20260731-02203008.bmp</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>12610</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20260731-02212149.bmp</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>12610</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>7c91c043db8ad51abd19dc25db45c114ed82aa0b8a070b4c086f16de758987eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20260731-02212685.bmp</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>12610</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>8567fecb4e010507f0d0f523eb1b24d1728a7cc0e0da740bf7a6f50101742348</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20260731-02353123.bmp</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>12610</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2d6adaf59d0d7fbc708d13081d3f17088f2fbf4bcd294594c6c75a9eb977ced9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20260731-02353746.bmp</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>12610</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>08b99076996fe11fef7a2a04ae5d79425fc561734a1ce191f7a552f79cb54870</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20260731-02353859.bmp</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>12610</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20260731-02354044.bmp</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>12610</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20260731-02370471.bmp</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>12610</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>a6c294878e92faf157d8dbab26978a947a0f1a6bb7a5caf9d0d47e7e8832f993</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2027-07-30_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20260731-02371008.bmp</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>12610</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>9788007b93e3e88a13fe4ef3770fc9384705eecfeda18ff08de4e1e7dac6abcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20260731-14043166.bmp</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>12610</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2d6adaf59d0d7fbc708d13081d3f17088f2fbf4bcd294594c6c75a9eb977ced9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20260731-14043896.bmp</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>12610</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08b99076996fe11fef7a2a04ae5d79425fc561734a1ce191f7a552f79cb54870</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20260731-14044086.bmp</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>12610</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20260731-14044283.bmp</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>12610</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20260731-14053513.bmp</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>12610</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7c91c043db8ad51abd19dc25db45c114ed82aa0b8a070b4c086f16de758987eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42n RC2+</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20260731-14054045.bmp</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>12610</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>8567fecb4e010507f0d0f523eb1b24d1728a7cc0e0da740bf7a6f50101742348</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20260731-14212239.bmp</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>12610</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2d6adaf59d0d7fbc708d13081d3f17088f2fbf4bcd294594c6c75a9eb977ced9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20260731-14212775.bmp</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>12610</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>08b99076996fe11fef7a2a04ae5d79425fc561734a1ce191f7a552f79cb54870</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>20260731-14212846.bmp</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>12610</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20260731-14212956.bmp</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>12610</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>f282d27183f8d3601196d5e48b6a457ace22a2e49a5ea88d05e234a4681073cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20260731-14225352.bmp</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>12610</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>a6c294878e92faf157d8dbab26978a947a0f1a6bb7a5caf9d0d47e7e8832f993</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2027-07-31_001 DM42 RC2+</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>6</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>20260731-14225871.bmp</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>12610</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>9788007b93e3e88a13fe4ef3770fc9384705eecfeda18ff08de4e1e7dac6abcc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>